--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -8971,7 +8971,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>KG모빌리언스</t>
+          <t>KG파이낸셜</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -11855,7 +11855,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>씨어스테크놀로지</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -12723,7 +12723,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>엔씨소프트</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -17795,7 +17795,7 @@
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>대유에이텍</t>
+          <t>디와이에이</t>
         </is>
       </c>
       <c r="B1275" t="inlineStr">
@@ -18635,7 +18635,7 @@
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>디이엔티</t>
+          <t>APS이노베이션</t>
         </is>
       </c>
       <c r="B1345" t="inlineStr">
@@ -23843,7 +23843,7 @@
     <row r="1779">
       <c r="A1779" t="inlineStr">
         <is>
-          <t>이노와이어리스</t>
+          <t>LIG아큐버</t>
         </is>
       </c>
       <c r="B1779" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -2342,7 +2342,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TPC</t>
+          <t>TPC로보틱스</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>에코바이오</t>
+          <t>에코심플렉스</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -32870,7 +32870,7 @@
     <row r="1792">
       <c r="A1792" t="inlineStr">
         <is>
-          <t>이엠코리아</t>
+          <t>신화프리텍</t>
         </is>
       </c>
       <c r="B1792" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -13409,7 +13409,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>대성파인텍</t>
+          <t>디에스엠</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -26141,7 +26141,7 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>모코엠시스</t>
+          <t>이노테나</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
@@ -34358,7 +34358,7 @@
     <row r="1880">
       <c r="A1880" t="inlineStr">
         <is>
-          <t>케이바이오</t>
+          <t>케이바이오랩스</t>
         </is>
       </c>
       <c r="B1880" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -15879,7 +15879,7 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>씨메스</t>
+          <t>씨메스로보틱스</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -30001,7 +30001,7 @@
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>에스엠코어</t>
+          <t>엠엑스로보틱스</t>
         </is>
       </c>
       <c r="B1623" t="inlineStr">
@@ -31017,7 +31017,7 @@
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>엠투아이</t>
+          <t>엠엑스온</t>
         </is>
       </c>
       <c r="B1683" t="inlineStr">
@@ -32632,7 +32632,7 @@
     <row r="1778">
       <c r="A1778" t="inlineStr">
         <is>
-          <t>이노룰스</t>
+          <t>이노에이엑스</t>
         </is>
       </c>
       <c r="B1778" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -7409,7 +7409,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>위너스</t>
+          <t>위너스일렉</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -22303,7 +22303,7 @@
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>SPC삼립</t>
+          <t>삼립</t>
         </is>
       </c>
       <c r="B1169" t="inlineStr">
@@ -29903,7 +29903,7 @@
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>에스씨엠생명과학</t>
+          <t>풍전약품</t>
         </is>
       </c>
       <c r="B1617" t="inlineStr">
@@ -31731,7 +31731,7 @@
     <row r="1725">
       <c r="A1725" t="inlineStr">
         <is>
-          <t>우리이앤엘</t>
+          <t>우리이앤엘하루틴</t>
         </is>
       </c>
       <c r="B1725" t="inlineStr">
@@ -34256,7 +34256,7 @@
     <row r="1874">
       <c r="A1874" t="inlineStr">
         <is>
-          <t>캐리소프트</t>
+          <t>에피소드컴퍼니</t>
         </is>
       </c>
       <c r="B1874" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -7751,7 +7751,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>유투바이오</t>
+          <t>지구홀딩스</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -12820,7 +12820,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>국전약품</t>
+          <t>국전</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -32258,7 +32258,7 @@
     <row r="1756">
       <c r="A1756" t="inlineStr">
         <is>
-          <t>위니아에이드</t>
+          <t>큐에이드</t>
         </is>
       </c>
       <c r="B1756" t="inlineStr">
@@ -33533,7 +33533,7 @@
     <row r="1831">
       <c r="A1831" t="inlineStr">
         <is>
-          <t>제이스텍</t>
+          <t>제이스로보틱스</t>
         </is>
       </c>
       <c r="B1831" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -24781,7 +24781,7 @@
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>동아화성</t>
+          <t>SY동아</t>
         </is>
       </c>
       <c r="B1315" t="inlineStr">
@@ -35480,7 +35480,7 @@
     <row r="1946">
       <c r="A1946" t="inlineStr">
         <is>
-          <t>파수</t>
+          <t>파수에이아이</t>
         </is>
       </c>
       <c r="B1946" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -23425,7 +23425,7 @@
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>네오펙트</t>
+          <t>다이나믹솔루션</t>
         </is>
       </c>
       <c r="B1235" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -5038,7 +5038,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>삼화페인트공업</t>
+          <t>SP삼화</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -30171,7 +30171,7 @@
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>에스퓨얼셀</t>
+          <t>에스프리즘</t>
         </is>
       </c>
       <c r="B1633" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -1297,7 +1297,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>시알홀딩스</t>
+          <t>CR홀딩스</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1373,7 +1373,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>F&amp;F 홀딩스</t>
+          <t>F&amp;F홀딩스</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1696,7 +1696,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>케이씨티시</t>
+          <t>KCTC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4981,7 +4981,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>삼화전자공업</t>
+          <t>삼화전자</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5000,7 +5000,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>삼화콘덴서공업</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7732,7 +7732,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>유진증권</t>
+          <t>유진투자증권</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -10696,7 +10696,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>한국ANKOR유전</t>
+          <t>한국투자ANKOR유전해외자원개발특별자산투자회사1호(지분증권)</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -10772,7 +10772,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>한국석유공업</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -10810,7 +10810,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>한국전력공사</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -11000,7 +11000,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>한신기계공업</t>
+          <t>한신기계</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -11494,7 +11494,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>휴니드테크놀러지스</t>
+          <t>휴니드</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -12022,7 +12022,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>케이티앤지</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -12250,7 +12250,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>엘에스일렉트릭</t>
+          <t>LS ELECTRIC</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -12497,7 +12497,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>에스케이바이오팜</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -12744,7 +12744,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>계룡건설산업</t>
+          <t>계룡건설</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -13827,7 +13827,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>롯데칠성음료</t>
+          <t>롯데칠성</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -14815,7 +14815,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>삼성화재해상보험</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -15632,7 +15632,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>신세계I&amp;C</t>
+          <t>신세계 I&amp;C</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>엑스큐어</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20841,7 +20841,7 @@
     <row r="1083">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>태양금속공업</t>
+          <t>태양금속</t>
         </is>
       </c>
       <c r="B1083" t="inlineStr">
@@ -21181,7 +21181,7 @@
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>디아이동일</t>
+          <t>DI동일</t>
         </is>
       </c>
       <c r="B1103" t="inlineStr">
@@ -21657,7 +21657,7 @@
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>케이씨씨</t>
+          <t>KCC</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
@@ -21861,7 +21861,7 @@
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>엘에스일렉트릭</t>
+          <t>LS ELECTRIC</t>
         </is>
       </c>
       <c r="B1143" t="inlineStr">
@@ -21997,7 +21997,7 @@
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>엔피씨</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="B1151" t="inlineStr">
@@ -22184,7 +22184,7 @@
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>에스제이엠</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="B1162" t="inlineStr">
@@ -22201,7 +22201,7 @@
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>에스제이엠홀딩스</t>
+          <t>SJM홀딩스</t>
         </is>
       </c>
       <c r="B1163" t="inlineStr">
@@ -22371,7 +22371,7 @@
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>티케이지휴켐스</t>
+          <t>TKG휴켐스</t>
         </is>
       </c>
       <c r="B1173" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>서울도시가스</t>
+          <t>서울가스</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
@@ -27501,7 +27501,7 @@
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>서울리거</t>
+          <t>코스리거글로벌</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
@@ -27552,7 +27552,7 @@
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>서울식품공업</t>
+          <t>서울식품</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
@@ -28024,7 +28024,7 @@
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>케이티스카이라이프</t>
+          <t>스카이라이프</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
@@ -28309,7 +28309,7 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>신세계I&amp;C</t>
+          <t>신세계 I&amp;C</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>엘브이엠씨</t>
+          <t>엘브이엠씨홀딩스</t>
         </is>
       </c>
       <c r="B1670" t="inlineStr">
@@ -32360,7 +32360,7 @@
     <row r="1762">
       <c r="A1762" t="inlineStr">
         <is>
-          <t>유나이티드</t>
+          <t>유나이티드제약</t>
         </is>
       </c>
       <c r="B1762" t="inlineStr">
@@ -36704,7 +36704,7 @@
     <row r="2018">
       <c r="A2018" t="inlineStr">
         <is>
-          <t>한국단자공업</t>
+          <t>한국단자</t>
         </is>
       </c>
       <c r="B2018" t="inlineStr">
@@ -36942,7 +36942,7 @@
     <row r="2032">
       <c r="A2032" t="inlineStr">
         <is>
-          <t>한국주철관공업</t>
+          <t>한국주철관</t>
         </is>
       </c>
       <c r="B2032" t="inlineStr">
@@ -38196,7 +38196,7 @@
     <row r="2106">
       <c r="A2106" t="inlineStr">
         <is>
-          <t>현대자동차</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="B2106" t="inlineStr">
@@ -38413,7 +38413,7 @@
     <row r="2119">
       <c r="A2119" t="inlineStr">
         <is>
-          <t>화승인더스트리</t>
+          <t>화승인더</t>
         </is>
       </c>
       <c r="B2119" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>엑스큐어</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -23663,7 +23663,7 @@
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>농우바이오</t>
+          <t>NH농우바이오</t>
         </is>
       </c>
       <c r="B1249" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -35480,7 +35480,7 @@
     <row r="1946">
       <c r="A1946" t="inlineStr">
         <is>
-          <t>파수에이아이</t>
+          <t>파수AI</t>
         </is>
       </c>
       <c r="B1946" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>엑스큐어</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -18003,7 +18003,7 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>이스트아시아홀딩스</t>
+          <t>딥커머스</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -29648,7 +29648,7 @@
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>애머릿지</t>
+          <t>파이온엑스</t>
         </is>
       </c>
       <c r="B1602" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>엑스큐어</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -8834,7 +8834,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>차백신연구소</t>
+          <t>아리바이오랩</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>엑스큐어</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -35769,7 +35769,7 @@
     <row r="1963">
       <c r="A1963" t="inlineStr">
         <is>
-          <t>푸른기술</t>
+          <t>푸른로보틱스</t>
         </is>
       </c>
       <c r="B1963" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>엑스큐어</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>아이로보틱스</t>
+          <t>금강제강</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>엑스큐어</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>금강제강</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -33057,7 +33057,7 @@
     <row r="1803">
       <c r="A1803" t="inlineStr">
         <is>
-          <t>인스코비</t>
+          <t>프리티</t>
         </is>
       </c>
       <c r="B1803" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -752,7 +752,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>씨아이에스</t>
+          <t>SFA넥셀</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>엑스큐어</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>아이로보틱스</t>
+          <t>금강제강</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -7713,7 +7713,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>유일에너테크</t>
+          <t>성원에너텍</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>엑스큐어</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>공구우먼</t>
+          <t>나인앤컴퍼니</t>
         </is>
       </c>
       <c r="B1190" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>금강제강</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -29478,7 +29478,7 @@
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>알로이스</t>
+          <t>아틀라스링크</t>
         </is>
       </c>
       <c r="B1592" t="inlineStr">
@@ -30290,7 +30290,7 @@
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>에이비프로바이오</t>
+          <t>루트K</t>
         </is>
       </c>
       <c r="B1640" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -1943,7 +1943,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NPX</t>
+          <t>엔피엑스</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>엑스큐어</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>아이로보틱스</t>
+          <t>금강제강</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>엑스큐어</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>금강제강</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -3986,7 +3986,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>동원금속</t>
+          <t>동원모빌리티</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -10886,7 +10886,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>한글과컴퓨터</t>
+          <t>한컴</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>엑스큐어</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -17623,7 +17623,7 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>우정바이오</t>
+          <t>콜마바이오텍</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>아이로보틱스</t>
+          <t>금강제강</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -5608,7 +5608,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>소룩스</t>
+          <t>아리바이오홀딩스</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>엑스큐어</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -23136,7 +23136,7 @@
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>나무기술</t>
+          <t>나무에이엑스</t>
         </is>
       </c>
       <c r="B1218" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>금강제강</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -37958,7 +37958,7 @@
     <row r="2092">
       <c r="A2092" t="inlineStr">
         <is>
-          <t>핸디소프트</t>
+          <t>폴라리스AI핸디</t>
         </is>
       </c>
       <c r="B2092" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>퀀텀레일</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>아이로보틱스</t>
+          <t>금강제강</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -6554,7 +6554,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>압타머사이언스</t>
+          <t>츌립앤사이언스</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>퀀텀레일</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>금강제강</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -30745,7 +30745,7 @@
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>엔피</t>
+          <t>컴투스엔</t>
         </is>
       </c>
       <c r="B1667" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -6402,7 +6402,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>알엔티엑스</t>
+          <t>MSDI</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>메가스터디</t>
+          <t>퀀텀레일</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온로보틱스</t>
+          <t>라온텍</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>아이로보틱스</t>
+          <t>금강제강</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피씨디렉트</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>힘스</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">

--- a/시그널뷰_기업개요.xlsx
+++ b/시그널뷰_기업개요.xlsx
@@ -10487,7 +10487,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17019,7 +17019,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>퀀텀레일</t>
+          <t>메가스터디</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -20283,7 +20283,7 @@
     <row r="1051">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1051" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>라온텍</t>
+          <t>라온로보틱스</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -26719,7 +26719,7 @@
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
@@ -29019,7 +29019,7 @@
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>금강제강</t>
+          <t>아이로보틱스</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -36024,7 +36024,7 @@
     <row r="1978">
       <c r="A1978" t="inlineStr">
         <is>
-          <t>플레이그램</t>
+          <t>MDS스피어</t>
         </is>
       </c>
       <c r="B1978" t="inlineStr">
@@ -36075,7 +36075,7 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>피씨디렉트</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
@@ -38804,7 +38804,7 @@
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>힘스</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B2142" t="inlineStr">
